--- a/survey_templates/037_mobile_app_usage_survey--survey_templates.xlsx
+++ b/survey_templates/037_mobile_app_usage_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Every day'}</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment'}</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment'}</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'productivity'}</t>
+          <t>productivity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Productivity'}</t>
+          <t>Productivity</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'gaming'}</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Gaming'}</t>
+          <t>Gaming</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'navigation'}</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Navigation'}</t>
+          <t>Navigation</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'convenience'}</t>
+          <t>convenience</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Convenience'}</t>
+          <t>Convenience</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment'}</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment'}</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'productivity'}</t>
+          <t>productivity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Productivity'}</t>
+          <t>Productivity</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'navigation'}</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Navigation'}</t>
+          <t>Navigation</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'design'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Design'}</t>
+          <t>Design</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'performance'}</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Performance'}</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'functionality'}</t>
+          <t>functionality</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Functionality'}</t>
+          <t>Functionality</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'user_interface'}</t>
+          <t>user_interface</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'User Interface'}</t>
+          <t>User Interface</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'easy_to_use'}</t>
+          <t>easy_to_use</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Easy to use'}</t>
+          <t>Easy to use</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'intuitive'}</t>
+          <t>intuitive</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Intuitive'}</t>
+          <t>Intuitive</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'fast'}</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Fast'}</t>
+          <t>Fast</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'simple'}</t>
+          <t>simple</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Simple'}</t>
+          <t>Simple</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'slow_performance'}</t>
+          <t>slow_performance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Slow performance'}</t>
+          <t>Slow performance</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'confusing_design'}</t>
+          <t>confusing_design</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Confusing design'}</t>
+          <t>Confusing design</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'difficult_to_use'}</t>
+          <t>difficult_to_use</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Difficult to use'}</t>
+          <t>Difficult to use</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_hour'}</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 hour'}</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_hours'}</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': '1-2 hours'}</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'2-4_hours'}</t>
+          <t>2-4_hours</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': '2-4 hours'}</t>
+          <t>2-4 hours</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'4-6_hours'}</t>
+          <t>4-6_hours</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': '4-6 hours'}</t>
+          <t>4-6 hours</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_6_hours'}</t>
+          <t>more_than_6_hours</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'More than 6 hours'}</t>
+          <t>More than 6 hours</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'ios'}</t>
+          <t>ios</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'iOS'}</t>
+          <t>iOS</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'android'}</t>
+          <t>android</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Android'}</t>
+          <t>Android</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_phone'}</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile phone'}</t>
+          <t>Mobile phone</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_phone'}</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile phone'}</t>
+          <t>Mobile phone</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'watch'}</t>
+          <t>watch</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Watch'}</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
